--- a/docs/oc-mensuales/suministro-de-combustibles/jul-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10968.44</v>
+        <v>11072.63</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3759.52</v>
+        <v>3795.23</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>11815.63</v>
+        <v>11927.87</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5907.82</v>
+        <v>5963.93</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2308.85</v>
+        <v>2330.78</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5240.77</v>
+        <v>5290.55</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>19334.67</v>
+        <v>19518.33</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2685.37</v>
+        <v>2710.88</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10741.48</v>
+        <v>10843.52</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3759.52</v>
+        <v>3795.23</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4296.59</v>
+        <v>4337.41</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>18259.45</v>
+        <v>18432.89</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6444.89</v>
+        <v>6506.11</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3692.92</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2363.13</v>
+        <v>2385.57</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2470.54</v>
+        <v>2494.01</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21482.97</v>
+        <v>21687.03</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2792.79</v>
+        <v>2819.31</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15145.49</v>
+        <v>15289.36</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4296.59</v>
+        <v>4337.41</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2304.24</v>
+        <v>2326.13</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2363.13</v>
+        <v>2385.57</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10669.52</v>
+        <v>10770.87</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2309.42</v>
+        <v>2331.36</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2909.76</v>
+        <v>2937.4</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4833.67</v>
+        <v>4879.58</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>9559.92</v>
+        <v>9650.73</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2309.42</v>
+        <v>2331.36</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5370.74</v>
+        <v>5421.76</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5370.74</v>
+        <v>5421.76</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>10741.48</v>
+        <v>10843.52</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3222.45</v>
+        <v>3253.06</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3222.45</v>
+        <v>3253.06</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2416.83</v>
+        <v>2439.79</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10741.48</v>
+        <v>10783.42</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>15038.08</v>
+        <v>15096.78</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2470.54</v>
+        <v>2480.19</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>19334.67</v>
+        <v>19410.15</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.71</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4827.59</v>
+        <v>4846.43</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8626.73</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5907.82</v>
+        <v>5930.88</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.71</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>6616.75</v>
+        <v>6642.58</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4296.59</v>
+        <v>4313.37</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2682.15</v>
+        <v>2692.62</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>32224.45</v>
+        <v>32350.25</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8626.73</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4073.17</v>
+        <v>4089.07</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>4296.59</v>
+        <v>4313.37</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.71</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>19334.67</v>
+        <v>19410.15</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7519.04</v>
+        <v>7548.39</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2951.03</v>
+        <v>2962.55</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>13963.93</v>
+        <v>14018.44</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2685.37</v>
+        <v>2695.85</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7502.93</v>
+        <v>7532.22</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2685.37</v>
+        <v>2695.85</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4618.84</v>
+        <v>4636.87</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2363.13</v>
+        <v>2372.35</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9130.26</v>
+        <v>9165.9</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2309.42</v>
+        <v>2318.43</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>6444.89</v>
+        <v>6470.05</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5267.09</v>
+        <v>5287.65</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>38404.03</v>
+        <v>38553.94</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>11269.11</v>
+        <v>11313.1</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>32918.35</v>
+        <v>33046.85</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3759.52</v>
+        <v>3774.2</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>40817.64</v>
+        <v>40976.98</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>13963.93</v>
+        <v>14018.44</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>8056.11</v>
+        <v>8087.56</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2363.13</v>
+        <v>2386.89</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4296.59</v>
+        <v>4339.81</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7519.04</v>
+        <v>7594.66</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>10741.48</v>
+        <v>10849.52</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8679.610000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3222.45</v>
+        <v>3254.86</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2309.42</v>
+        <v>2332.65</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5370.74</v>
+        <v>5424.76</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4296.59</v>
+        <v>4339.81</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3222.45</v>
+        <v>3254.86</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4661.8</v>
+        <v>4708.69</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>16112.23</v>
+        <v>16274.28</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2685.37</v>
+        <v>2712.38</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2470.54</v>
+        <v>2495.39</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>32224.45</v>
+        <v>32548.55</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>5370.74</v>
+        <v>5424.76</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>16112.23</v>
+        <v>16274.28</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>13426.86</v>
+        <v>13561.9</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8679.610000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>6444.89</v>
+        <v>6509.71</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>15038.08</v>
+        <v>15189.32</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2685.37</v>
+        <v>2712.38</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2363.13</v>
+        <v>2386.89</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5370.74</v>
+        <v>5424.76</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>7519.04</v>
+        <v>7594.66</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>7519.04</v>
+        <v>7594.66</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>10677.04</v>
+        <v>10784.42</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>7519.04</v>
+        <v>7594.66</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3222.45</v>
+        <v>3254.86</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6822.99</v>
+        <v>6891.61</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4833.67</v>
+        <v>4882.28</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2685.37</v>
+        <v>2712.38</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2685.37</v>
+        <v>2712.38</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6444.89</v>
+        <v>6509.71</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8056.11</v>
+        <v>8137.14</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5370.74</v>
+        <v>5424.76</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5110.19</v>
+        <v>5161.36</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2363.13</v>
+        <v>2386.79</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2363.13</v>
+        <v>2386.79</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5102.21</v>
+        <v>5153.3</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>16112.23</v>
+        <v>16273.57</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2812.12</v>
+        <v>2840.28</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8679.24</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3222.45</v>
+        <v>3254.71</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4296.59</v>
+        <v>4339.62</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4081.76</v>
+        <v>4122.64</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>12889.78</v>
+        <v>13018.86</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>7650.94</v>
+        <v>7727.56</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2309.42</v>
+        <v>2332.54</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3759.52</v>
+        <v>3797.17</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2309.42</v>
+        <v>2332.54</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>5717.02</v>
+        <v>5774.26</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6981.97</v>
+        <v>7051.88</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2685.37</v>
+        <v>2712.26</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3866.93</v>
+        <v>3905.66</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5370.74</v>
+        <v>5424.52</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5370.74</v>
+        <v>5424.52</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>7519.04</v>
+        <v>7594.33</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2309.42</v>
+        <v>2332.54</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>7666.06</v>
+        <v>7742.83</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3222.45</v>
+        <v>3254.71</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>12889.78</v>
+        <v>13018.86</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>10741.48</v>
+        <v>10849.05</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>13963.93</v>
+        <v>14103.76</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>53707.42</v>
+        <v>54245.23</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>16112.23</v>
+        <v>16273.57</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>4296.59</v>
+        <v>4339.62</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>76039.98</v>
+        <v>76801.42</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>5965.52</v>
+        <v>5995.91</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6444.89</v>
+        <v>6477.73</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2363.13</v>
+        <v>2375.17</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6444.89</v>
+        <v>6477.73</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7519.04</v>
+        <v>7557.35</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3759.52</v>
+        <v>3778.68</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2685.37</v>
+        <v>2699.06</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>5370.74</v>
+        <v>5398.11</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2363.13</v>
+        <v>2375.17</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>32224.45</v>
+        <v>32388.66</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>42965.94</v>
+        <v>43184.89</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>4511.42</v>
+        <v>4534.41</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>48336.68</v>
+        <v>48583</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>12889.78</v>
+        <v>12955.47</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5907.82</v>
+        <v>5937.92</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>16112.23</v>
+        <v>16194.33</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>156825.68</v>
+        <v>157624.83</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2470.54</v>
+        <v>2483.13</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4296.59</v>
+        <v>4318.49</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3813.23</v>
+        <v>3832.66</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>12889.78</v>
+        <v>12955.47</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>12387.08</v>
+        <v>12450.2</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3222.45</v>
+        <v>3238.87</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>22377.74</v>
+        <v>22491.77</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3222.45</v>
+        <v>3238.87</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>10741.48</v>
+        <v>10796.22</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4296.59</v>
+        <v>4313.32</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8626.639999999999</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>4511.42</v>
+        <v>4528.99</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>4726.25</v>
+        <v>4744.65</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4296.59</v>
+        <v>4313.32</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>19334.67</v>
+        <v>19409.94</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3759.52</v>
+        <v>3774.15</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2363.13</v>
+        <v>2372.33</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>10741.48</v>
+        <v>10783.3</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>4189.18</v>
+        <v>4205.49</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>10677.04</v>
+        <v>10718.6</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>10741.48</v>
+        <v>10783.3</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2792.79</v>
+        <v>2803.66</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>8056.11</v>
+        <v>8087.47</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2363.13</v>
+        <v>2372.33</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>12889.78</v>
+        <v>12939.96</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>268537.12</v>
+        <v>269582.47</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>18260.52</v>
+        <v>18331.61</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5263.33</v>
+        <v>5283.82</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2309.42</v>
+        <v>2318.41</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4696.31</v>
+        <v>4714.6</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3222.45</v>
+        <v>3234.99</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>24493.72</v>
+        <v>24589.07</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>6813.32</v>
+        <v>6839.85</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>12889.78</v>
+        <v>12824.49</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2309.42</v>
+        <v>2297.72</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2685.37</v>
+        <v>2671.77</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>35446.9</v>
+        <v>35267.34</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2309.42</v>
+        <v>2297.72</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>13963.93</v>
+        <v>13893.19</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>4296.59</v>
+        <v>4274.83</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5370.74</v>
+        <v>5343.54</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>5689.96</v>
+        <v>5661.14</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>9667.34</v>
+        <v>9618.360000000001</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>4972.6</v>
+        <v>4947.41</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2363.13</v>
+        <v>2351.16</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8549.66</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>6444.89</v>
+        <v>6412.24</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>16917.84</v>
+        <v>16832.14</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3583.46</v>
+        <v>3565.3</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2309.42</v>
+        <v>2297.72</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>10741.48</v>
+        <v>10687.07</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>4833.67</v>
+        <v>4809.18</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>26853.71</v>
+        <v>26717.68</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>13963.93</v>
+        <v>13893.19</v>
       </c>
     </row>
     <row r="222">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>10741.48</v>
+        <v>10687.07</v>
       </c>
     </row>
     <row r="223">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2363.13</v>
+        <v>2351.16</v>
       </c>
     </row>
     <row r="224">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3222.45</v>
+        <v>3206.12</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4833.67</v>
+        <v>4809.18</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>3222.45</v>
+        <v>3206.12</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2470.54</v>
+        <v>2458.03</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>4296.59</v>
+        <v>4274.83</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>4296.59</v>
+        <v>4274.83</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2685.37</v>
+        <v>2671.77</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2308.85</v>
+        <v>2297.15</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>3866.93</v>
+        <v>3847.35</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>5800.4</v>
+        <v>5771.02</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>9426.52</v>
+        <v>9378.77</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>37595.2</v>
+        <v>37675.32</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.31</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>34365.23</v>
+        <v>34438.48</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>7519.04</v>
+        <v>7535.06</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>10741.48</v>
+        <v>10764.38</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2685.37</v>
+        <v>2691.09</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>6444.89</v>
+        <v>6458.63</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>5370.74</v>
+        <v>5382.19</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="245">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>3044.52</v>
+        <v>3051.01</v>
       </c>
     </row>
     <row r="246">
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>4296.59</v>
+        <v>4305.75</v>
       </c>
     </row>
     <row r="247">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2470.54</v>
+        <v>2475.81</v>
       </c>
     </row>
     <row r="248">
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>35446.9</v>
+        <v>35522.45</v>
       </c>
     </row>
     <row r="249">
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>35446.9</v>
+        <v>35522.45</v>
       </c>
     </row>
     <row r="250">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>6670.46</v>
+        <v>6684.68</v>
       </c>
     </row>
     <row r="251">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9209.99</v>
+        <v>9229.620000000001</v>
       </c>
     </row>
     <row r="252">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>5155.91</v>
+        <v>5166.9</v>
       </c>
     </row>
     <row r="253">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>10741.48</v>
+        <v>10764.38</v>
       </c>
     </row>
     <row r="254">
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.31</v>
       </c>
     </row>
     <row r="255">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>12818.71</v>
+        <v>12846.03</v>
       </c>
     </row>
     <row r="256">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>16112.23</v>
+        <v>16146.57</v>
       </c>
     </row>
     <row r="257">
@@ -16132,7 +16132,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.31</v>
       </c>
     </row>
     <row r="258">
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>6122.65</v>
+        <v>6135.7</v>
       </c>
     </row>
     <row r="259">
@@ -16254,7 +16254,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="260">
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2308.85</v>
+        <v>2313.77</v>
       </c>
     </row>
     <row r="261">
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>26853.71</v>
+        <v>26910.95</v>
       </c>
     </row>
     <row r="262">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>17186.38</v>
+        <v>17223.01</v>
       </c>
     </row>
     <row r="263">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>10741.48</v>
+        <v>10764.38</v>
       </c>
     </row>
     <row r="264">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>4833.67</v>
+        <v>4843.97</v>
       </c>
     </row>
     <row r="265">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="266">
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>21482.97</v>
+        <v>21528.76</v>
       </c>
     </row>
     <row r="267">
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2470.54</v>
+        <v>2475.81</v>
       </c>
     </row>
     <row r="268">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>4214.32</v>
+        <v>4223.3</v>
       </c>
     </row>
     <row r="269">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>3007.62</v>
+        <v>3014.03</v>
       </c>
     </row>
     <row r="270">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2790.13</v>
+        <v>2796.08</v>
       </c>
     </row>
     <row r="271">
@@ -16986,7 +16986,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4833.67</v>
+        <v>4843.97</v>
       </c>
     </row>
     <row r="272">
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2685.37</v>
+        <v>2691.09</v>
       </c>
     </row>
     <row r="273">
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>13963.93</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="274">
@@ -17169,7 +17169,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>5370.74</v>
+        <v>5382.19</v>
       </c>
     </row>
     <row r="275">
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>10741.48</v>
+        <v>10764.38</v>
       </c>
     </row>
     <row r="276">
@@ -17291,7 +17291,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8611.5</v>
       </c>
     </row>
     <row r="277">
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>32224.45</v>
+        <v>32293.14</v>
       </c>
     </row>
     <row r="278">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>12782.37</v>
+        <v>12865.7</v>
       </c>
     </row>
     <row r="279">
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>13587.98</v>
+        <v>13676.56</v>
       </c>
     </row>
     <row r="280">
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>16112.23</v>
+        <v>16217.27</v>
       </c>
     </row>
     <row r="281">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>4296.59</v>
+        <v>4324.6</v>
       </c>
     </row>
     <row r="282">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>5370.74</v>
+        <v>5405.76</v>
       </c>
     </row>
     <row r="283">
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>17186.38</v>
+        <v>17298.42</v>
       </c>
     </row>
     <row r="284">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>32224.45</v>
+        <v>32434.54</v>
       </c>
     </row>
     <row r="285">
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4618.84</v>
+        <v>4648.95</v>
       </c>
     </row>
     <row r="286">
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2857.5</v>
+        <v>2876.13</v>
       </c>
     </row>
     <row r="287">
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>10911.2</v>
+        <v>10982.33</v>
       </c>
     </row>
     <row r="288">
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>7227.95</v>
+        <v>7275.07</v>
       </c>
     </row>
     <row r="289">
@@ -18084,7 +18084,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4296.59</v>
+        <v>4324.6</v>
       </c>
     </row>
     <row r="290">
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>6444.89</v>
+        <v>6486.91</v>
       </c>
     </row>
     <row r="291">
@@ -18206,7 +18206,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2309.42</v>
+        <v>2324.48</v>
       </c>
     </row>
     <row r="292">
@@ -18267,7 +18267,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>10741.48</v>
+        <v>10811.51</v>
       </c>
     </row>
     <row r="293">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>15789.98</v>
+        <v>15892.92</v>
       </c>
     </row>
     <row r="294">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>9237.68</v>
+        <v>9297.9</v>
       </c>
     </row>
     <row r="295">
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>6981.97</v>
+        <v>7027.48</v>
       </c>
     </row>
     <row r="296">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3222.45</v>
+        <v>3243.45</v>
       </c>
     </row>
     <row r="297">
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8649.209999999999</v>
       </c>
     </row>
     <row r="298">
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2685.37</v>
+        <v>2702.88</v>
       </c>
     </row>
     <row r="299">
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2685.37</v>
+        <v>2702.88</v>
       </c>
     </row>
     <row r="300">
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>10741.48</v>
+        <v>10811.51</v>
       </c>
     </row>
     <row r="301">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>40280.57</v>
+        <v>40372.94</v>
       </c>
     </row>
     <row r="302">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>38345.38</v>
+        <v>38433.31</v>
       </c>
     </row>
     <row r="303">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>4296.59</v>
+        <v>4306.45</v>
       </c>
     </row>
     <row r="304">
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2685.37</v>
+        <v>2691.53</v>
       </c>
     </row>
     <row r="305">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>9640.48</v>
+        <v>9662.59</v>
       </c>
     </row>
     <row r="306">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>37595.2</v>
+        <v>37681.41</v>
       </c>
     </row>
     <row r="307">
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>32224.45</v>
+        <v>32298.35</v>
       </c>
     </row>
     <row r="308">
@@ -19243,7 +19243,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.72</v>
       </c>
     </row>
     <row r="309">
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>8661.4</v>
+        <v>8681.26</v>
       </c>
     </row>
     <row r="310">
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>10741.48</v>
+        <v>10766.12</v>
       </c>
     </row>
     <row r="311">
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>9345.91</v>
+        <v>9367.35</v>
       </c>
     </row>
     <row r="312">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.84</v>
       </c>
     </row>
     <row r="313">
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>16112.23</v>
+        <v>16149.18</v>
       </c>
     </row>
     <row r="314">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>16112.23</v>
+        <v>16149.18</v>
       </c>
     </row>
     <row r="315">
@@ -19670,7 +19670,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>16112.23</v>
+        <v>16149.18</v>
       </c>
     </row>
     <row r="316">
@@ -19731,7 +19731,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.84</v>
       </c>
     </row>
     <row r="317">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.72</v>
       </c>
     </row>
     <row r="318">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2308.85</v>
+        <v>2314.14</v>
       </c>
     </row>
     <row r="319">
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>25303.41</v>
+        <v>25361.43</v>
       </c>
     </row>
     <row r="320">
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.72</v>
       </c>
     </row>
     <row r="321">
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3544.69</v>
+        <v>3552.82</v>
       </c>
     </row>
     <row r="322">
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>26853.71</v>
+        <v>26915.29</v>
       </c>
     </row>
     <row r="323">
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>4296.59</v>
+        <v>4306.45</v>
       </c>
     </row>
     <row r="324">
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>7519.04</v>
+        <v>7536.28</v>
       </c>
     </row>
     <row r="325">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4833.67</v>
+        <v>4844.75</v>
       </c>
     </row>
     <row r="326">
@@ -20341,7 +20341,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>34372.75</v>
+        <v>34451.57</v>
       </c>
     </row>
     <row r="327">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8612.889999999999</v>
       </c>
     </row>
     <row r="328">
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>4296.59</v>
+        <v>4306.45</v>
       </c>
     </row>
     <row r="329">
@@ -20524,7 +20524,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2685.37</v>
+        <v>2691.53</v>
       </c>
     </row>
     <row r="330">
@@ -20585,7 +20585,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2308.85</v>
+        <v>2314.14</v>
       </c>
     </row>
     <row r="331">
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>21482.97</v>
+        <v>21532.23</v>
       </c>
     </row>
     <row r="332">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8612.889999999999</v>
       </c>
     </row>
     <row r="333">
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5370.74</v>
+        <v>5383.06</v>
       </c>
     </row>
     <row r="334">
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.84</v>
       </c>
     </row>
     <row r="335">
@@ -20890,7 +20890,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>16112.23</v>
+        <v>16149.18</v>
       </c>
     </row>
     <row r="336">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>21482.97</v>
+        <v>21532.23</v>
       </c>
     </row>
     <row r="337">
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>19334.67</v>
+        <v>19379.01</v>
       </c>
     </row>
     <row r="338">
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>6928.26</v>
+        <v>6944.15</v>
       </c>
     </row>
     <row r="339">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>6981.97</v>
+        <v>6997.98</v>
       </c>
     </row>
     <row r="340">
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>5253.92</v>
+        <v>5265.97</v>
       </c>
     </row>
     <row r="341">
@@ -21256,7 +21256,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>26853.71</v>
+        <v>26915.29</v>
       </c>
     </row>
     <row r="342">
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>7519.04</v>
+        <v>7536.28</v>
       </c>
     </row>
     <row r="343">
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>12889.78</v>
+        <v>12919.34</v>
       </c>
     </row>
     <row r="344">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>6204.28</v>
+        <v>6218.51</v>
       </c>
     </row>
     <row r="345">
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>6444.89</v>
+        <v>6459.67</v>
       </c>
     </row>
     <row r="346">
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2363.13</v>
+        <v>2368.55</v>
       </c>
     </row>
     <row r="347">
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>7519.04</v>
+        <v>7536.28</v>
       </c>
     </row>
     <row r="348">
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>5370.74</v>
+        <v>5383.06</v>
       </c>
     </row>
     <row r="349">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>12889.78</v>
+        <v>12919.34</v>
       </c>
     </row>
     <row r="350">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2309.82</v>
+        <v>2315.11</v>
       </c>
     </row>
     <row r="351">
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>10741.48</v>
+        <v>10766.12</v>
       </c>
     </row>
     <row r="352">
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>9556.219999999999</v>
+        <v>9578.129999999999</v>
       </c>
     </row>
     <row r="353">
@@ -21988,7 +21988,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.84</v>
       </c>
     </row>
     <row r="354">
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>15038.08</v>
+        <v>15072.56</v>
       </c>
     </row>
     <row r="355">
@@ -22110,7 +22110,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>15341.78</v>
+        <v>15376.96</v>
       </c>
     </row>
     <row r="356">
@@ -22171,7 +22171,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2309.42</v>
+        <v>2324.88</v>
       </c>
     </row>
     <row r="357">
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>3222.45</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="358">
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>10848.9</v>
+        <v>10921.52</v>
       </c>
     </row>
     <row r="359">
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>4296.59</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="360">
@@ -22415,7 +22415,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2308.85</v>
+        <v>2324.3</v>
       </c>
     </row>
     <row r="361">
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8650.709999999999</v>
       </c>
     </row>
     <row r="362">
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2685.37</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="363">
@@ -22598,7 +22598,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>4833.67</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="364">
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2685.37</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="365">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>6444.89</v>
+        <v>6488.03</v>
       </c>
     </row>
     <row r="366">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>3823.97</v>
+        <v>3849.56</v>
       </c>
     </row>
     <row r="367">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>2308.85</v>
+        <v>2324.3</v>
       </c>
     </row>
     <row r="368">
@@ -22903,7 +22903,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>6036.54</v>
+        <v>6076.94</v>
       </c>
     </row>
     <row r="369">
@@ -22964,7 +22964,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>7304.21</v>
+        <v>7353.1</v>
       </c>
     </row>
     <row r="370">
@@ -23025,7 +23025,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>16297.08</v>
+        <v>16406.16</v>
       </c>
     </row>
     <row r="371">
@@ -23086,7 +23086,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>3222.45</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="372">
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>2309.42</v>
+        <v>2324.88</v>
       </c>
     </row>
     <row r="373">
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>6960.48</v>
+        <v>7007.07</v>
       </c>
     </row>
     <row r="374">
@@ -23269,7 +23269,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>10777.15</v>
+        <v>10849.28</v>
       </c>
     </row>
     <row r="375">
@@ -23330,7 +23330,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>3222.45</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="376">
@@ -23391,7 +23391,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="377">
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>35124.65</v>
+        <v>35359.76</v>
       </c>
     </row>
     <row r="378">
@@ -23513,7 +23513,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>21482.97</v>
+        <v>21626.77</v>
       </c>
     </row>
     <row r="379">
@@ -23574,7 +23574,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="380">
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>4684.36</v>
+        <v>4715.72</v>
       </c>
     </row>
     <row r="381">
@@ -23696,7 +23696,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4296.59</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="382">
@@ -23757,7 +23757,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>2308.85</v>
+        <v>2324.3</v>
       </c>
     </row>
     <row r="383">
@@ -23818,7 +23818,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8650.709999999999</v>
       </c>
     </row>
     <row r="384">
@@ -23879,7 +23879,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>5585.57</v>
+        <v>5622.96</v>
       </c>
     </row>
     <row r="385">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2363.13</v>
+        <v>2378.94</v>
       </c>
     </row>
     <row r="386">
@@ -24001,7 +24001,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>3007.62</v>
+        <v>3027.75</v>
       </c>
     </row>
     <row r="387">
@@ -24062,7 +24062,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>5112.95</v>
+        <v>5147.17</v>
       </c>
     </row>
     <row r="388">
@@ -24123,7 +24123,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="389">
@@ -24184,7 +24184,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>5203.52</v>
+        <v>5238.35</v>
       </c>
     </row>
     <row r="390">
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>7669.42</v>
+        <v>7720.76</v>
       </c>
     </row>
     <row r="391">
@@ -24306,7 +24306,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>10741.48</v>
+        <v>10813.38</v>
       </c>
     </row>
     <row r="392">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>49623.02</v>
+        <v>49955.18</v>
       </c>
     </row>
     <row r="393">
@@ -24428,7 +24428,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>35555.32</v>
+        <v>35793.31</v>
       </c>
     </row>
     <row r="394">
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3222.45</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="395">
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2308.85</v>
+        <v>2324.3</v>
       </c>
     </row>
     <row r="396">
@@ -24611,7 +24611,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>16112.23</v>
+        <v>16220.07</v>
       </c>
     </row>
     <row r="397">
@@ -24672,7 +24672,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>4296.59</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="398">
@@ -24733,7 +24733,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>4511.42</v>
+        <v>4541.62</v>
       </c>
     </row>
     <row r="399">
@@ -24794,7 +24794,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>7519.04</v>
+        <v>7569.37</v>
       </c>
     </row>
     <row r="400">
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>4296.59</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="401">
@@ -24916,7 +24916,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>3222.45</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="402">
@@ -24977,7 +24977,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2685.37</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="403">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>16112.23</v>
+        <v>16220.07</v>
       </c>
     </row>
     <row r="404">
@@ -25099,7 +25099,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>4296.59</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="405">
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>4833.67</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="406">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>3007.62</v>
+        <v>3027.75</v>
       </c>
     </row>
     <row r="407">
@@ -25282,7 +25282,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>16112.23</v>
+        <v>16220.07</v>
       </c>
     </row>
     <row r="408">
@@ -25343,7 +25343,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>21482.97</v>
+        <v>21626.77</v>
       </c>
     </row>
     <row r="409">
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>10741.48</v>
+        <v>10813.38</v>
       </c>
     </row>
     <row r="410">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>10741.48</v>
+        <v>10813.38</v>
       </c>
     </row>
     <row r="411">
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="412">
@@ -25587,7 +25587,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2308.85</v>
+        <v>2324.3</v>
       </c>
     </row>
     <row r="413">
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2309.42</v>
+        <v>2324.88</v>
       </c>
     </row>
     <row r="414">
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2363.13</v>
+        <v>2378.94</v>
       </c>
     </row>
     <row r="415">
@@ -25770,7 +25770,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3007.62</v>
+        <v>3027.75</v>
       </c>
     </row>
     <row r="416">
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="417">
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>6444.89</v>
+        <v>6488.03</v>
       </c>
     </row>
     <row r="418">
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>2363.13</v>
+        <v>2379.66</v>
       </c>
     </row>
     <row r="419">
@@ -26014,7 +26014,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>5955.08</v>
+        <v>5996.76</v>
       </c>
     </row>
     <row r="420">
@@ -26075,7 +26075,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2803.42</v>
+        <v>2823.04</v>
       </c>
     </row>
     <row r="421">
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>3222.45</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="422">
@@ -26197,7 +26197,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>5370.74</v>
+        <v>5408.33</v>
       </c>
     </row>
     <row r="423">
@@ -26258,7 +26258,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>11815.63</v>
+        <v>11898.32</v>
       </c>
     </row>
     <row r="424">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>5370.74</v>
+        <v>5408.33</v>
       </c>
     </row>
     <row r="425">
@@ -26380,7 +26380,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>3759.52</v>
+        <v>3785.83</v>
       </c>
     </row>
     <row r="426">
@@ -26441,7 +26441,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2685.37</v>
+        <v>2704.16</v>
       </c>
     </row>
     <row r="427">
@@ -26502,7 +26502,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>16112.23</v>
+        <v>16224.99</v>
       </c>
     </row>
     <row r="428">
@@ -26563,7 +26563,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>7472.1</v>
+        <v>7524.39</v>
       </c>
     </row>
     <row r="429">
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>3866.93</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="430">
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>16112.23</v>
+        <v>16224.99</v>
       </c>
     </row>
     <row r="431">
@@ -26746,7 +26746,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>9237.68</v>
+        <v>9302.33</v>
       </c>
     </row>
     <row r="432">
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2309.42</v>
+        <v>2325.58</v>
       </c>
     </row>
     <row r="433">
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>6444.89</v>
+        <v>6489.99</v>
       </c>
     </row>
     <row r="434">
@@ -26929,7 +26929,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>2470.54</v>
+        <v>2487.83</v>
       </c>
     </row>
     <row r="435">
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>5370.74</v>
+        <v>5408.33</v>
       </c>
     </row>
     <row r="436">
@@ -27051,7 +27051,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>39749.33</v>
+        <v>40027.51</v>
       </c>
     </row>
     <row r="437">
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>10741.48</v>
+        <v>10816.66</v>
       </c>
     </row>
     <row r="438">
@@ -27173,7 +27173,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>17186.38</v>
+        <v>17306.65</v>
       </c>
     </row>
     <row r="439">
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2363.13</v>
+        <v>2379.66</v>
       </c>
     </row>
     <row r="440">
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>14071.34</v>
+        <v>14169.82</v>
       </c>
     </row>
     <row r="441">
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8653.33</v>
       </c>
     </row>
     <row r="442">
@@ -27417,7 +27417,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>4522.73</v>
+        <v>4554.38</v>
       </c>
     </row>
     <row r="443">
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>12674.95</v>
+        <v>12763.66</v>
       </c>
     </row>
     <row r="444">
@@ -27539,7 +27539,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>2363.13</v>
+        <v>2379.66</v>
       </c>
     </row>
     <row r="445">
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>5370.74</v>
+        <v>5408.33</v>
       </c>
     </row>
     <row r="446">
@@ -27661,7 +27661,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>8056.11</v>
+        <v>8112.49</v>
       </c>
     </row>
     <row r="447">
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>10741.48</v>
+        <v>10816.66</v>
       </c>
     </row>
     <row r="448">
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>7696.17</v>
+        <v>7671.86</v>
       </c>
     </row>
     <row r="449">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>7519.04</v>
+        <v>7495.29</v>
       </c>
     </row>
     <row r="450">
@@ -27905,7 +27905,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>2309.42</v>
+        <v>2302.12</v>
       </c>
     </row>
     <row r="451">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>7519.04</v>
+        <v>7495.29</v>
       </c>
     </row>
     <row r="452">
@@ -28027,7 +28027,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>10741.48</v>
+        <v>10707.56</v>
       </c>
     </row>
     <row r="453">
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>16917.84</v>
+        <v>16864.4</v>
       </c>
     </row>
     <row r="454">
@@ -28149,7 +28149,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>11815.63</v>
+        <v>11778.31</v>
       </c>
     </row>
     <row r="455">
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>4081.13</v>
+        <v>4068.24</v>
       </c>
     </row>
     <row r="456">
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>2363.13</v>
+        <v>2355.66</v>
       </c>
     </row>
     <row r="457">
@@ -28332,7 +28332,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2685.37</v>
+        <v>2676.89</v>
       </c>
     </row>
     <row r="458">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>2685.37</v>
+        <v>2676.89</v>
       </c>
     </row>
     <row r="459">
@@ -28454,7 +28454,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>4296.59</v>
+        <v>4283.02</v>
       </c>
     </row>
     <row r="460">
@@ -28515,7 +28515,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>36521.05</v>
+        <v>36405.69</v>
       </c>
     </row>
     <row r="461">
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>22020.04</v>
+        <v>21950.49</v>
       </c>
     </row>
     <row r="462">
@@ -28637,7 +28637,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>21482.97</v>
+        <v>21415.11</v>
       </c>
     </row>
     <row r="463">
@@ -28698,7 +28698,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>13963.93</v>
+        <v>13919.82</v>
       </c>
     </row>
     <row r="464">
@@ -28759,7 +28759,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>22557.12</v>
+        <v>22485.87</v>
       </c>
     </row>
     <row r="465">
@@ -28820,7 +28820,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>10204.41</v>
+        <v>10172.18</v>
       </c>
     </row>
     <row r="466">
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>2685.37</v>
+        <v>2676.89</v>
       </c>
     </row>
     <row r="467">
@@ -28942,7 +28942,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>16304.85</v>
+        <v>16253.34</v>
       </c>
     </row>
     <row r="468">
@@ -29003,7 +29003,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>24490.59</v>
+        <v>24413.23</v>
       </c>
     </row>
     <row r="469">
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>42965.94</v>
+        <v>42830.22</v>
       </c>
     </row>
     <row r="470">
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>42965.94</v>
+        <v>42830.22</v>
       </c>
     </row>
     <row r="471">
@@ -29186,7 +29186,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>2685.37</v>
+        <v>2676.89</v>
       </c>
     </row>
     <row r="472">
@@ -29247,7 +29247,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>5370.74</v>
+        <v>5353.78</v>
       </c>
     </row>
     <row r="473">
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>32224.45</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="474">
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>2308.85</v>
+        <v>2301.56</v>
       </c>
     </row>
     <row r="475">
@@ -29430,7 +29430,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>2310.49</v>
+        <v>2303.2</v>
       </c>
     </row>
     <row r="476">
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>2534.11</v>
+        <v>2526.1</v>
       </c>
     </row>
     <row r="477">
@@ -29552,7 +29552,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>6444.89</v>
+        <v>6424.53</v>
       </c>
     </row>
     <row r="478">
@@ -29613,7 +29613,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>21482.97</v>
+        <v>21415.11</v>
       </c>
     </row>
     <row r="479">
@@ -29674,7 +29674,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>10741.48</v>
+        <v>10718.11</v>
       </c>
     </row>
     <row r="480">
@@ -29735,7 +29735,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>2363.13</v>
+        <v>2357.98</v>
       </c>
     </row>
     <row r="481">
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>10741.48</v>
+        <v>10718.11</v>
       </c>
     </row>
     <row r="482">
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2416.83</v>
+        <v>2411.58</v>
       </c>
     </row>
     <row r="483">
@@ -29918,7 +29918,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2363.13</v>
+        <v>2357.98</v>
       </c>
     </row>
     <row r="484">
@@ -29979,7 +29979,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>4833.67</v>
+        <v>4823.15</v>
       </c>
     </row>
     <row r="485">
@@ -30040,7 +30040,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>26842.43</v>
+        <v>26784.03</v>
       </c>
     </row>
     <row r="486">
@@ -30101,7 +30101,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>18455.48</v>
+        <v>18415.33</v>
       </c>
     </row>
     <row r="487">
@@ -30162,7 +30162,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>5370.74</v>
+        <v>5359.06</v>
       </c>
     </row>
     <row r="488">
@@ -30223,7 +30223,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>38347.1</v>
+        <v>38263.67</v>
       </c>
     </row>
     <row r="489">
@@ -30284,7 +30284,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>2308.85</v>
+        <v>2303.83</v>
       </c>
     </row>
     <row r="490">
@@ -30345,7 +30345,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>13426.86</v>
+        <v>13397.64</v>
       </c>
     </row>
     <row r="491">
@@ -30406,7 +30406,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2685.37</v>
+        <v>2679.53</v>
       </c>
     </row>
     <row r="492">
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>6444.89</v>
+        <v>6430.87</v>
       </c>
     </row>
     <row r="493">
@@ -30528,7 +30528,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>10741.48</v>
+        <v>10718.11</v>
       </c>
     </row>
     <row r="494">
@@ -30589,7 +30589,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>6444.89</v>
+        <v>6430.87</v>
       </c>
     </row>
     <row r="495">
@@ -30650,7 +30650,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>5370.74</v>
+        <v>5359.06</v>
       </c>
     </row>
     <row r="496">
@@ -30711,7 +30711,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>13963.93</v>
+        <v>13933.55</v>
       </c>
     </row>
     <row r="497">
@@ -30772,7 +30772,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8574.49</v>
       </c>
     </row>
     <row r="498">
@@ -30833,7 +30833,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>12889.78</v>
+        <v>12861.74</v>
       </c>
     </row>
     <row r="499">
@@ -30894,7 +30894,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2384.34</v>
+        <v>2379.15</v>
       </c>
     </row>
     <row r="500">
@@ -30955,7 +30955,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>5370.74</v>
+        <v>5359.06</v>
       </c>
     </row>
     <row r="501">
@@ -31016,7 +31016,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>9882.17</v>
+        <v>9860.66</v>
       </c>
     </row>
     <row r="502">
@@ -31077,7 +31077,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>10741.48</v>
+        <v>10718.11</v>
       </c>
     </row>
     <row r="503">
@@ -31138,7 +31138,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>4296.59</v>
+        <v>4287.25</v>
       </c>
     </row>
     <row r="504">
@@ -31199,7 +31199,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>10741.48</v>
+        <v>10718.11</v>
       </c>
     </row>
     <row r="505">
@@ -31260,7 +31260,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>32224.45</v>
+        <v>32154.34</v>
       </c>
     </row>
     <row r="506">
@@ -31321,7 +31321,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>2308.85</v>
+        <v>2304.22</v>
       </c>
     </row>
     <row r="507">
@@ -31382,7 +31382,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>10311.83</v>
+        <v>10291.15</v>
       </c>
     </row>
     <row r="508">
@@ -31443,7 +31443,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>5370.74</v>
+        <v>5359.98</v>
       </c>
     </row>
     <row r="509">
@@ -31504,7 +31504,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>12889.78</v>
+        <v>12863.94</v>
       </c>
     </row>
     <row r="510">
@@ -31565,7 +31565,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2685.37</v>
+        <v>2679.99</v>
       </c>
     </row>
     <row r="511">
@@ -31626,7 +31626,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>8056.11</v>
+        <v>8039.96</v>
       </c>
     </row>
     <row r="512">
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2363.13</v>
+        <v>2358.39</v>
       </c>
     </row>
     <row r="513">
@@ -31748,7 +31748,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>3222.45</v>
+        <v>3215.99</v>
       </c>
     </row>
     <row r="514">
@@ -31809,7 +31809,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>10741.48</v>
+        <v>10719.95</v>
       </c>
     </row>
     <row r="515">
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2363.13</v>
+        <v>2358.39</v>
       </c>
     </row>
     <row r="516">
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>2309.42</v>
+        <v>2304.79</v>
       </c>
     </row>
     <row r="517">
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>3222.45</v>
+        <v>3215.99</v>
       </c>
     </row>
     <row r="518">
@@ -32053,7 +32053,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>21482.97</v>
+        <v>21439.9</v>
       </c>
     </row>
     <row r="519">
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>9667.34</v>
+        <v>9647.959999999999</v>
       </c>
     </row>
     <row r="520">
@@ -32175,7 +32175,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>14207.76</v>
+        <v>14179.28</v>
       </c>
     </row>
     <row r="521">
@@ -32236,7 +32236,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>32224.45</v>
+        <v>32159.86</v>
       </c>
     </row>
     <row r="522">
@@ -32297,7 +32297,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2685.37</v>
+        <v>2679.99</v>
       </c>
     </row>
     <row r="523">
@@ -32358,7 +32358,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2309.42</v>
+        <v>2304.79</v>
       </c>
     </row>
     <row r="524">
@@ -32419,7 +32419,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>21482.97</v>
+        <v>21439.9</v>
       </c>
     </row>
     <row r="525">
@@ -32480,7 +32480,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>2685.37</v>
+        <v>2679.99</v>
       </c>
     </row>
     <row r="526">
@@ -32541,7 +32541,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>2277.19</v>
+        <v>2272.63</v>
       </c>
     </row>
     <row r="527">
@@ -32602,7 +32602,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8575.959999999999</v>
       </c>
     </row>
     <row r="528">
@@ -32663,7 +32663,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>58004.02</v>
+        <v>57887.74</v>
       </c>
     </row>
     <row r="529">
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>32224.45</v>
+        <v>32159.86</v>
       </c>
     </row>
     <row r="530">
@@ -32785,7 +32785,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>21482.97</v>
+        <v>21439.9</v>
       </c>
     </row>
     <row r="531">
@@ -32846,7 +32846,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>3222.45</v>
+        <v>3215.99</v>
       </c>
     </row>
     <row r="532">
@@ -32907,7 +32907,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>53707.42</v>
+        <v>53599.76</v>
       </c>
     </row>
     <row r="533">
@@ -32968,7 +32968,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>10741.48</v>
+        <v>10719.95</v>
       </c>
     </row>
     <row r="534">
@@ -33029,7 +33029,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>7519.04</v>
+        <v>7503.97</v>
       </c>
     </row>
     <row r="535">
@@ -33090,7 +33090,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>9882.17</v>
+        <v>9862.360000000001</v>
       </c>
     </row>
     <row r="536">
@@ -33151,7 +33151,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>23631.27</v>
+        <v>23583.89</v>
       </c>
     </row>
     <row r="537">
@@ -33212,7 +33212,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>5371.48</v>
+        <v>5360.71</v>
       </c>
     </row>
     <row r="538">
@@ -33273,7 +33273,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>12352.71</v>
+        <v>12327.94</v>
       </c>
     </row>
     <row r="539">
@@ -33334,7 +33334,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>7519.04</v>
+        <v>7503.97</v>
       </c>
     </row>
     <row r="540">
@@ -33395,7 +33395,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>10741.48</v>
+        <v>10719.95</v>
       </c>
     </row>
     <row r="541">
@@ -33456,7 +33456,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2309.42</v>
+        <v>2304.79</v>
       </c>
     </row>
     <row r="542">
@@ -33517,7 +33517,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>21482.97</v>
+        <v>21439.9</v>
       </c>
     </row>
     <row r="543">
@@ -33578,7 +33578,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>5370.74</v>
+        <v>5339.66</v>
       </c>
     </row>
     <row r="544">
@@ -33639,7 +33639,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>4824.7</v>
+        <v>4796.77</v>
       </c>
     </row>
     <row r="545">
@@ -33700,7 +33700,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>16112.23</v>
+        <v>16018.97</v>
       </c>
     </row>
     <row r="546">
@@ -33761,7 +33761,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>2308.85</v>
+        <v>2295.49</v>
       </c>
     </row>
     <row r="547">
@@ -33822,7 +33822,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>10741.48</v>
+        <v>10679.31</v>
       </c>
     </row>
     <row r="548">
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>5240.77</v>
+        <v>5210.44</v>
       </c>
     </row>
     <row r="549">
@@ -33944,7 +33944,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>15038.08</v>
+        <v>14951.04</v>
       </c>
     </row>
     <row r="550">
@@ -34005,7 +34005,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>5370.74</v>
+        <v>5339.66</v>
       </c>
     </row>
     <row r="551">
@@ -34066,7 +34066,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>2363.13</v>
+        <v>2349.45</v>
       </c>
     </row>
     <row r="552">
@@ -34127,7 +34127,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>3222.45</v>
+        <v>3203.79</v>
       </c>
     </row>
     <row r="553">
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>3222.45</v>
+        <v>3203.79</v>
       </c>
     </row>
     <row r="554">
@@ -34249,7 +34249,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>4833.67</v>
+        <v>4805.69</v>
       </c>
     </row>
     <row r="555">
@@ -34310,7 +34310,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>5660.7</v>
+        <v>5627.93</v>
       </c>
     </row>
     <row r="556">
@@ -34371,7 +34371,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2363.13</v>
+        <v>2349.45</v>
       </c>
     </row>
     <row r="557">
@@ -34432,7 +34432,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>3222.45</v>
+        <v>3203.79</v>
       </c>
     </row>
     <row r="558">
@@ -34493,7 +34493,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>3222.45</v>
+        <v>3203.79</v>
       </c>
     </row>
     <row r="559">
@@ -34554,7 +34554,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>30076.16</v>
+        <v>29902.07</v>
       </c>
     </row>
     <row r="560">
@@ -34615,7 +34615,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2309.42</v>
+        <v>2296.05</v>
       </c>
     </row>
     <row r="561">
@@ -34676,7 +34676,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>2647.81</v>
+        <v>2632.48</v>
       </c>
     </row>
     <row r="562">
@@ -34737,7 +34737,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>4833.67</v>
+        <v>4805.69</v>
       </c>
     </row>
     <row r="563">
@@ -34798,7 +34798,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8543.450000000001</v>
       </c>
     </row>
     <row r="564">
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>2685.37</v>
+        <v>2669.83</v>
       </c>
     </row>
     <row r="565">
@@ -34920,7 +34920,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>11074.47</v>
+        <v>11010.37</v>
       </c>
     </row>
     <row r="566">
@@ -34981,7 +34981,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>5370.74</v>
+        <v>5339.66</v>
       </c>
     </row>
     <row r="567">
@@ -35042,7 +35042,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>9667.34</v>
+        <v>9611.379999999999</v>
       </c>
     </row>
     <row r="568">
@@ -35103,7 +35103,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>10741.48</v>
+        <v>10679.31</v>
       </c>
     </row>
     <row r="569">
@@ -35164,7 +35164,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>5079.59</v>
+        <v>5050.19</v>
       </c>
     </row>
     <row r="570">
@@ -35225,7 +35225,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>4224.72</v>
+        <v>4200.27</v>
       </c>
     </row>
     <row r="571">
@@ -35286,7 +35286,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>5370.74</v>
+        <v>5339.66</v>
       </c>
     </row>
     <row r="572">
@@ -35347,7 +35347,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>4668.95</v>
+        <v>4641.92</v>
       </c>
     </row>
     <row r="573">
@@ -35408,7 +35408,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>10741.48</v>
+        <v>10568.14</v>
       </c>
     </row>
     <row r="574">
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>18259.83</v>
+        <v>17965.16</v>
       </c>
     </row>
     <row r="575">
@@ -35530,7 +35530,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>2717.6</v>
+        <v>2673.74</v>
       </c>
     </row>
     <row r="576">
@@ -35591,7 +35591,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>35446.9</v>
+        <v>34874.87</v>
       </c>
     </row>
     <row r="577">
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>17723.45</v>
+        <v>17437.44</v>
       </c>
     </row>
     <row r="578">
@@ -35713,7 +35713,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>2308.85</v>
+        <v>2271.59</v>
       </c>
     </row>
     <row r="579">
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>11278.56</v>
+        <v>11096.55</v>
       </c>
     </row>
     <row r="580">
@@ -35835,7 +35835,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>9667.34</v>
+        <v>9511.33</v>
       </c>
     </row>
     <row r="581">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>3222.45</v>
+        <v>3170.44</v>
       </c>
     </row>
     <row r="582">
@@ -35957,7 +35957,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>11740.44</v>
+        <v>11550.98</v>
       </c>
     </row>
     <row r="583">
@@ -36018,7 +36018,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>5753.34</v>
+        <v>5660.5</v>
       </c>
     </row>
     <row r="584">
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8454.51</v>
       </c>
     </row>
     <row r="585">
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2363.13</v>
+        <v>2324.99</v>
       </c>
     </row>
     <row r="586">
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>2309.42</v>
+        <v>2272.15</v>
       </c>
     </row>
     <row r="587">
@@ -36262,7 +36262,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2309.42</v>
+        <v>2272.15</v>
       </c>
     </row>
     <row r="588">
@@ -36323,7 +36323,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>8378.360000000001</v>
+        <v>8243.15</v>
       </c>
     </row>
     <row r="589">
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>26853.71</v>
+        <v>26420.36</v>
       </c>
     </row>
     <row r="590">
@@ -36445,7 +36445,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>7696.17</v>
+        <v>7571.97</v>
       </c>
     </row>
     <row r="591">
@@ -36506,7 +36506,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>3222.45</v>
+        <v>3170.44</v>
       </c>
     </row>
     <row r="592">
@@ -36567,7 +36567,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>3759.52</v>
+        <v>3698.85</v>
       </c>
     </row>
     <row r="593">
@@ -36628,7 +36628,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2309.42</v>
+        <v>2272.15</v>
       </c>
     </row>
     <row r="594">
@@ -36689,7 +36689,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>3759.52</v>
+        <v>3698.85</v>
       </c>
     </row>
     <row r="595">
@@ -36750,7 +36750,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>32224.45</v>
+        <v>31704.43</v>
       </c>
     </row>
     <row r="596">
@@ -36811,7 +36811,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>7519.04</v>
+        <v>7397.7</v>
       </c>
     </row>
     <row r="597">
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>10741.48</v>
+        <v>10568.14</v>
       </c>
     </row>
     <row r="598">
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>3329.86</v>
+        <v>3276.12</v>
       </c>
     </row>
     <row r="599">
@@ -36994,7 +36994,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>4296.59</v>
+        <v>4227.26</v>
       </c>
     </row>
     <row r="600">
@@ -37055,7 +37055,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>6444.89</v>
+        <v>6340.89</v>
       </c>
     </row>
     <row r="601">
@@ -37116,7 +37116,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>3222.45</v>
+        <v>3170.44</v>
       </c>
     </row>
     <row r="602">
@@ -37177,7 +37177,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8454.51</v>
       </c>
     </row>
     <row r="603">
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>4941.08</v>
+        <v>4861.86</v>
       </c>
     </row>
     <row r="604">
@@ -37299,7 +37299,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>4511.42</v>
+        <v>4439.09</v>
       </c>
     </row>
     <row r="605">
@@ -37360,7 +37360,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2309.42</v>
+        <v>2272.39</v>
       </c>
     </row>
     <row r="606">
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>2363.13</v>
+        <v>2325.24</v>
       </c>
     </row>
     <row r="607">
@@ -37482,7 +37482,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>7196.79</v>
+        <v>7081.4</v>
       </c>
     </row>
     <row r="608">
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>4404.01</v>
+        <v>4333.4</v>
       </c>
     </row>
     <row r="609">
@@ -37604,7 +37604,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>4296.59</v>
+        <v>4227.7</v>
       </c>
     </row>
     <row r="610">
@@ -37665,7 +37665,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>4833.67</v>
+        <v>4756.17</v>
       </c>
     </row>
     <row r="611">
@@ -37726,7 +37726,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>12674.95</v>
+        <v>12471.73</v>
       </c>
     </row>
     <row r="612">
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>10569.73</v>
+        <v>10400.26</v>
       </c>
     </row>
     <row r="613">
@@ -37848,7 +37848,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>28937.77</v>
+        <v>28473.8</v>
       </c>
     </row>
     <row r="614">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>4833.67</v>
+        <v>4756.17</v>
       </c>
     </row>
     <row r="615">
@@ -37970,7 +37970,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2363.13</v>
+        <v>2325.24</v>
       </c>
     </row>
     <row r="616">
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>3759.52</v>
+        <v>3699.24</v>
       </c>
     </row>
     <row r="617">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>3222.45</v>
+        <v>3170.78</v>
       </c>
     </row>
     <row r="618">
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>5907.82</v>
+        <v>5813.09</v>
       </c>
     </row>
     <row r="619">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>10740.02</v>
+        <v>10567.82</v>
       </c>
     </row>
     <row r="620">
@@ -38275,7 +38275,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>4296.59</v>
+        <v>4227.7</v>
       </c>
     </row>
     <row r="621">
@@ -38336,7 +38336,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>32224.45</v>
+        <v>31707.78</v>
       </c>
     </row>
     <row r="622">
@@ -38397,7 +38397,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>7696.17</v>
+        <v>7572.77</v>
       </c>
     </row>
     <row r="623">
@@ -38458,7 +38458,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>2308.85</v>
+        <v>2271.83</v>
       </c>
     </row>
     <row r="624">
@@ -38519,7 +38519,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>2363.13</v>
+        <v>2325.24</v>
       </c>
     </row>
     <row r="625">
@@ -38580,7 +38580,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8455.41</v>
       </c>
     </row>
     <row r="626">
@@ -38641,7 +38641,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>6444.89</v>
+        <v>6341.56</v>
       </c>
     </row>
     <row r="627">
@@ -38702,7 +38702,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>2685.37</v>
+        <v>2642.32</v>
       </c>
     </row>
     <row r="628">
@@ -38763,7 +38763,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>6675.83</v>
+        <v>6568.8</v>
       </c>
     </row>
     <row r="629">
@@ -38824,7 +38824,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>2308.85</v>
+        <v>2271.83</v>
       </c>
     </row>
     <row r="630">
@@ -38885,7 +38885,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8493.200000000001</v>
       </c>
     </row>
     <row r="631">
@@ -38946,7 +38946,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>5370.74</v>
+        <v>5308.25</v>
       </c>
     </row>
     <row r="632">
@@ -39007,7 +39007,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>5112.95</v>
+        <v>5053.45</v>
       </c>
     </row>
     <row r="633">
@@ -39068,7 +39068,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>8056.11</v>
+        <v>7962.38</v>
       </c>
     </row>
     <row r="634">
@@ -39129,7 +39129,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2685.37</v>
+        <v>2654.13</v>
       </c>
     </row>
     <row r="635">
@@ -39190,7 +39190,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>10741.48</v>
+        <v>10616.5</v>
       </c>
     </row>
     <row r="636">
@@ -39251,7 +39251,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>10741.48</v>
+        <v>10616.5</v>
       </c>
     </row>
     <row r="637">
@@ -39312,7 +39312,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>6444.89</v>
+        <v>6369.9</v>
       </c>
     </row>
     <row r="638">
@@ -39373,7 +39373,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>26853.71</v>
+        <v>26541.25</v>
       </c>
     </row>
     <row r="639">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>21482.97</v>
+        <v>21233</v>
       </c>
     </row>
     <row r="640">
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>6444.89</v>
+        <v>6369.9</v>
       </c>
     </row>
     <row r="641">
@@ -39556,7 +39556,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>4296.59</v>
+        <v>4246.6</v>
       </c>
     </row>
     <row r="642">
@@ -39617,7 +39617,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>3222.45</v>
+        <v>3184.95</v>
       </c>
     </row>
     <row r="643">
@@ -39678,7 +39678,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>11815.63</v>
+        <v>11678.15</v>
       </c>
     </row>
     <row r="644">
@@ -39739,7 +39739,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>34372.75</v>
+        <v>33972.8</v>
       </c>
     </row>
     <row r="645">
@@ -39800,7 +39800,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>5540.75</v>
+        <v>5476.28</v>
       </c>
     </row>
     <row r="646">
@@ -39861,7 +39861,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>15038.08</v>
+        <v>14863.1</v>
       </c>
     </row>
     <row r="647">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>2685.37</v>
+        <v>2654.13</v>
       </c>
     </row>
     <row r="648">
@@ -39983,7 +39983,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>16343.21</v>
+        <v>16153.05</v>
       </c>
     </row>
     <row r="649">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>36521.05</v>
+        <v>36096.1</v>
       </c>
     </row>
     <row r="650">
@@ -40105,7 +40105,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>4296.59</v>
+        <v>4246.6</v>
       </c>
     </row>
     <row r="651">
@@ -40166,7 +40166,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>5370.74</v>
+        <v>5308.25</v>
       </c>
     </row>
     <row r="652">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>10741.48</v>
+        <v>10616.5</v>
       </c>
     </row>
     <row r="653">
@@ -40288,7 +40288,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>10789.82</v>
+        <v>10664.27</v>
       </c>
     </row>
     <row r="654">
@@ -40349,7 +40349,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>2363.13</v>
+        <v>2335.63</v>
       </c>
     </row>
     <row r="655">
@@ -40410,7 +40410,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>2309.42</v>
+        <v>2282.55</v>
       </c>
     </row>
     <row r="656">
@@ -40471,7 +40471,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>2974.32</v>
+        <v>2939.71</v>
       </c>
     </row>
     <row r="657">
@@ -40532,7 +40532,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>21482.97</v>
+        <v>21233</v>
       </c>
     </row>
     <row r="658">
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>2309.42</v>
+        <v>2282.55</v>
       </c>
     </row>
     <row r="659">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>2685.37</v>
+        <v>2670.48</v>
       </c>
     </row>
     <row r="660">
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>75190.39</v>
+        <v>74773.53999999999</v>
       </c>
     </row>
     <row r="661">
@@ -40776,7 +40776,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>10741.48</v>
+        <v>10681.93</v>
       </c>
     </row>
     <row r="662">
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>3222.45</v>
+        <v>3204.58</v>
       </c>
     </row>
     <row r="663">
@@ -40898,7 +40898,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>21482.97</v>
+        <v>21363.87</v>
       </c>
     </row>
     <row r="664">
@@ -40959,7 +40959,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>12889.78</v>
+        <v>12818.32</v>
       </c>
     </row>
     <row r="665">
@@ -41020,7 +41020,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>3222.45</v>
+        <v>3204.58</v>
       </c>
     </row>
     <row r="666">
@@ -41081,7 +41081,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>3834.71</v>
+        <v>3813.45</v>
       </c>
     </row>
     <row r="667">
@@ -41142,7 +41142,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>6444.89</v>
+        <v>6409.16</v>
       </c>
     </row>
     <row r="668">
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>3222.45</v>
+        <v>3204.58</v>
       </c>
     </row>
     <row r="669">
@@ -41264,7 +41264,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>5370.74</v>
+        <v>5340.97</v>
       </c>
     </row>
     <row r="670">
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>3222.45</v>
+        <v>3204.58</v>
       </c>
     </row>
     <row r="671">
@@ -41386,7 +41386,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>4833.67</v>
+        <v>4806.87</v>
       </c>
     </row>
     <row r="672">
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>3222.45</v>
+        <v>3204.58</v>
       </c>
     </row>
     <row r="673">
@@ -41508,7 +41508,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>10741.48</v>
+        <v>10681.93</v>
       </c>
     </row>
     <row r="674">
@@ -41569,7 +41569,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>2685.37</v>
+        <v>2670.48</v>
       </c>
     </row>
     <row r="675">
@@ -41630,7 +41630,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2363.13</v>
+        <v>2350.03</v>
       </c>
     </row>
     <row r="676">
@@ -41691,7 +41691,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2309.42</v>
+        <v>2296.62</v>
       </c>
     </row>
     <row r="677">
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>2363.13</v>
+        <v>2350.03</v>
       </c>
     </row>
     <row r="678">
@@ -41813,7 +41813,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>4296.59</v>
+        <v>4272.77</v>
       </c>
     </row>
     <row r="679">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>2363.13</v>
+        <v>2350.03</v>
       </c>
     </row>
     <row r="680">
@@ -41935,7 +41935,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>3329.86</v>
+        <v>3311.4</v>
       </c>
     </row>
     <row r="681">
@@ -41996,7 +41996,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>5370.74</v>
+        <v>5340.97</v>
       </c>
     </row>
     <row r="682">
@@ -42057,7 +42057,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>2685.37</v>
+        <v>2670.48</v>
       </c>
     </row>
     <row r="683">
@@ -42118,7 +42118,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>22557.12</v>
+        <v>22446.21</v>
       </c>
     </row>
     <row r="684">
@@ -42179,7 +42179,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>3222.45</v>
+        <v>3206.6</v>
       </c>
     </row>
     <row r="685">
@@ -42240,7 +42240,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>5870.22</v>
+        <v>5841.36</v>
       </c>
     </row>
     <row r="686">
@@ -42301,7 +42301,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>10741.48</v>
+        <v>10688.67</v>
       </c>
     </row>
     <row r="687">
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>22599.88</v>
+        <v>22488.77</v>
       </c>
     </row>
     <row r="688">
@@ -42423,7 +42423,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>2309.42</v>
+        <v>2298.06</v>
       </c>
     </row>
     <row r="689">
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>4296.59</v>
+        <v>4275.47</v>
       </c>
     </row>
     <row r="690">
@@ -42545,7 +42545,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>3222.45</v>
+        <v>3206.6</v>
       </c>
     </row>
     <row r="691">
@@ -42606,7 +42606,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>11815.63</v>
+        <v>11757.54</v>
       </c>
     </row>
     <row r="692">
@@ -42667,7 +42667,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>21482.97</v>
+        <v>21377.34</v>
       </c>
     </row>
     <row r="693">
@@ -42728,7 +42728,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>2308.85</v>
+        <v>2297.5</v>
       </c>
     </row>
     <row r="694">
@@ -42789,7 +42789,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>5370.74</v>
+        <v>5344.34</v>
       </c>
     </row>
     <row r="695">
@@ -42850,7 +42850,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>2309.42</v>
+        <v>2298.06</v>
       </c>
     </row>
     <row r="696">
@@ -42911,7 +42911,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>2309.42</v>
+        <v>2298.06</v>
       </c>
     </row>
     <row r="697">
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>19334.67</v>
+        <v>19239.61</v>
       </c>
     </row>
     <row r="698">
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>26853.71</v>
+        <v>26721.68</v>
       </c>
     </row>
     <row r="699">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>10741.48</v>
+        <v>10688.67</v>
       </c>
     </row>
     <row r="700">
@@ -43155,7 +43155,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>53707.42</v>
+        <v>53443.36</v>
       </c>
     </row>
     <row r="701">
@@ -43216,7 +43216,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>3222.45</v>
+        <v>3206.6</v>
       </c>
     </row>
     <row r="702">
@@ -43277,7 +43277,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>13963.93</v>
+        <v>13895.27</v>
       </c>
     </row>
     <row r="703">
@@ -43338,7 +43338,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>12889.78</v>
+        <v>12826.41</v>
       </c>
     </row>
     <row r="704">
@@ -43399,7 +43399,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>5370.74</v>
+        <v>5344.34</v>
       </c>
     </row>
     <row r="705">
@@ -43460,7 +43460,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>13426.86</v>
+        <v>13516.73</v>
       </c>
     </row>
     <row r="706">
@@ -43521,7 +43521,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>16112.23</v>
+        <v>16220.07</v>
       </c>
     </row>
     <row r="707">
@@ -43582,7 +43582,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>10741.48</v>
+        <v>10813.38</v>
       </c>
     </row>
     <row r="708">
@@ -43643,7 +43643,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>6477.65</v>
+        <v>6521.01</v>
       </c>
     </row>
     <row r="709">
@@ -43704,7 +43704,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>4941.08</v>
+        <v>4974.16</v>
       </c>
     </row>
     <row r="710">
@@ -43765,7 +43765,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>5585.57</v>
+        <v>5622.96</v>
       </c>
     </row>
     <row r="711">
@@ -43826,7 +43826,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>2685.37</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="712">
@@ -43887,7 +43887,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>2857.23</v>
+        <v>2876.36</v>
       </c>
     </row>
     <row r="713">
@@ -43948,7 +43948,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>2363.13</v>
+        <v>2378.94</v>
       </c>
     </row>
     <row r="714">
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="715">
@@ -44070,7 +44070,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="716">
@@ -44131,7 +44131,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>8270.940000000001</v>
+        <v>8326.299999999999</v>
       </c>
     </row>
     <row r="717">
@@ -44192,7 +44192,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="718">
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>2308.85</v>
+        <v>2324.3</v>
       </c>
     </row>
     <row r="719">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8650.709999999999</v>
       </c>
     </row>
     <row r="720">
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>5950.78</v>
+        <v>5990.61</v>
       </c>
     </row>
     <row r="721">
@@ -44436,7 +44436,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>3759.52</v>
+        <v>3784.68</v>
       </c>
     </row>
     <row r="722">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>10741.48</v>
+        <v>10813.38</v>
       </c>
     </row>
     <row r="723">
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>3222.45</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="724">
@@ -44619,7 +44619,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>4296.59</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="725">
@@ -44680,7 +44680,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="726">
@@ -44741,7 +44741,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>6659.72</v>
+        <v>6704.3</v>
       </c>
     </row>
     <row r="727">
@@ -44802,7 +44802,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>4350.3</v>
+        <v>4379.42</v>
       </c>
     </row>
     <row r="728">
@@ -44863,7 +44863,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>6444.89</v>
+        <v>6488.03</v>
       </c>
     </row>
     <row r="729">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>4296.59</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="730">
@@ -44985,7 +44985,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>2309.42</v>
+        <v>2324.88</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/jul-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21175,7 +21175,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31240,7 +31240,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32887,7 +32887,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -34229,7 +34229,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35693,7 +35693,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -36059,7 +36059,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36730,7 +36730,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36974,7 +36974,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37096,7 +37096,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -38255,7 +38255,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38438,7 +38438,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38804,7 +38804,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -39048,7 +39048,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39414,7 +39414,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39719,7 +39719,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39780,7 +39780,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -40024,7 +40024,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40634,7 +40634,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40756,7 +40756,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -41183,7 +41183,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41854,7 +41854,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -43379,7 +43379,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43623,7 +43623,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43928,7 +43928,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -44050,7 +44050,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/jul-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/jul-2026.xlsx
@@ -562,7 +562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10897,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +11092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +12067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12652,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12782,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12282,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12343,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12404,7 +13172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12465,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12526,7 +13302,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12587,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12648,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12709,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12831,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12892,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12953,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13014,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13075,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13136,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13197,7 +14017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13258,7 +14082,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13319,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13380,7 +14212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13441,7 +14277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13502,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13563,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13624,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13685,7 +14537,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13746,7 +14602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13807,7 +14667,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13868,7 +14732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13929,7 +14797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13990,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14051,7 +14927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14112,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14173,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14234,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14295,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14356,7 +15252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14417,7 +15317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14478,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14539,7 +15447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14600,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14661,7 +15577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14722,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14783,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14844,7 +15772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14905,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14966,7 +15902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15027,7 +15967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15088,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15210,7 +16162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15271,7 +16227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15332,7 +16292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15393,7 +16357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15454,7 +16422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15515,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15576,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15637,7 +16617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15698,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15759,7 +16747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15820,7 +16812,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15881,7 +16877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15942,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16003,7 +17007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16064,7 +17072,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16125,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16186,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16247,7 +17267,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16308,7 +17332,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16369,7 +17397,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16430,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16491,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17592,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16613,7 +17657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16674,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17917,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16918,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +18047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17040,7 +18112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +18177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17162,7 +18242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17223,7 +18307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17284,7 +18372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +18437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17467,7 +18567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17528,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17772,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17833,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17894,7 +19022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18016,7 +19152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18077,7 +19217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18138,7 +19282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18199,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18260,7 +19412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18321,7 +19477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18382,7 +19542,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18443,7 +19607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18504,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18565,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18626,7 +19802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18687,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18748,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18809,7 +19997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18870,7 +20062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18931,7 +20127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18992,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19053,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19114,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19175,7 +20387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19236,7 +20452,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19297,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19358,7 +20582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19419,7 +20647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19480,7 +20712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19541,7 +20777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19602,7 +20842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19663,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19724,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19785,7 +21037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19846,7 +21102,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19907,7 +21167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19968,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +21297,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20090,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20151,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20212,7 +21492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20273,7 +21557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20334,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20395,7 +21687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20456,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20517,7 +21817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20578,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20639,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20700,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20761,7 +22077,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20822,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20883,7 +22207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20944,7 +22272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21005,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21066,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21127,7 +22467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21188,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21249,7 +22597,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21310,7 +22662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21371,7 +22727,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21493,7 +22857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21554,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21615,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21676,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21737,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21798,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21859,7 +23247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21920,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21981,7 +23377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22042,7 +23442,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +23507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22164,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22225,7 +23637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22286,7 +23702,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22347,7 +23767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22408,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22469,7 +23897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22530,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +24027,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22652,7 +24092,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22713,7 +24157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22774,7 +24222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22835,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22896,7 +24352,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22957,7 +24417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23018,7 +24482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23079,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23140,7 +24612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23201,7 +24677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23262,7 +24742,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23323,7 +24807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23384,7 +24872,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23445,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23506,7 +25002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23567,7 +25067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23628,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23689,7 +25197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23750,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23811,7 +25327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23872,7 +25392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23933,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23994,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24055,7 +25587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24116,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24177,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24238,7 +25782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24299,7 +25847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24360,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24421,7 +25977,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24482,7 +26042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24543,7 +26107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24604,7 +26172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24665,7 +26237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24726,7 +26302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24787,7 +26367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24848,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24970,7 +26562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25031,7 +26627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25092,7 +26692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25153,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25214,7 +26822,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25275,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25336,7 +26952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25397,7 +27017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25458,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25519,7 +27147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25580,7 +27212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25641,7 +27277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25702,7 +27342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25763,7 +27407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25824,7 +27472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25885,7 +27537,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25946,7 +27602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26007,7 +27667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26068,7 +27732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26129,7 +27797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26190,7 +27862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26251,7 +27927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26312,7 +27992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26373,7 +28057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26434,7 +28122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26495,7 +28187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26556,7 +28252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26617,7 +28317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26678,7 +28382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26739,7 +28447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26800,7 +28512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26861,7 +28577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26922,7 +28642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26983,7 +28707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27044,7 +28772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27105,7 +28837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27166,7 +28902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27227,7 +28967,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27288,7 +29032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27349,7 +29097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27410,7 +29162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27471,7 +29227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27532,7 +29292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27593,7 +29357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27654,7 +29422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27715,7 +29487,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27776,7 +29552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27837,7 +29617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27898,7 +29682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27959,7 +29747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28020,7 +29812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28081,7 +29877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28142,7 +29942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28203,7 +30007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28264,7 +30072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28325,7 +30137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28386,7 +30202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28447,7 +30267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28508,7 +30332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28569,7 +30397,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28630,7 +30462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28691,7 +30527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28752,7 +30592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28813,7 +30657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28874,7 +30722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28935,7 +30787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28996,7 +30852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29057,7 +30917,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29118,7 +30982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29179,7 +31047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29240,7 +31112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29301,7 +31177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29362,7 +31242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29423,7 +31307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29484,7 +31372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29545,7 +31437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29606,7 +31502,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29667,7 +31567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29728,7 +31632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29789,7 +31697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29850,7 +31762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29911,7 +31827,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29972,7 +31892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30033,7 +31957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30094,7 +32022,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30155,7 +32087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30216,7 +32152,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30277,7 +32217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30338,7 +32282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30399,7 +32347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30460,7 +32412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30521,7 +32477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30582,7 +32542,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30643,7 +32607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30704,7 +32672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30765,7 +32737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30826,7 +32802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30887,7 +32867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30948,7 +32932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31009,7 +32997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31070,7 +33062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31131,7 +33127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31192,7 +33192,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31253,7 +33257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31314,7 +33322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31375,7 +33387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31436,7 +33452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31497,7 +33517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31558,7 +33582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31619,7 +33647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31680,7 +33712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31741,7 +33777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31802,7 +33842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31863,7 +33907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31924,7 +33972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31985,7 +34037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32046,7 +34102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32107,7 +34167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32168,7 +34232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32229,7 +34297,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32290,7 +34362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32351,7 +34427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32412,7 +34492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32473,7 +34557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32534,7 +34622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32595,7 +34687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32656,7 +34752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32717,7 +34817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32778,7 +34882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32839,7 +34947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32900,7 +35012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32961,7 +35077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33022,7 +35142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33083,7 +35207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33144,7 +35272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33205,7 +35337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33266,7 +35402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33327,7 +35467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33388,7 +35532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33449,7 +35597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33510,7 +35662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33571,7 +35727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33632,7 +35792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33693,7 +35857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33754,7 +35922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33815,7 +35987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33876,7 +36052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33937,7 +36117,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33998,7 +36182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34059,7 +36247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34120,7 +36312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34181,7 +36377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34242,7 +36442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34303,7 +36507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34364,7 +36572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34425,7 +36637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34486,7 +36702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34547,7 +36767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34608,7 +36832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34669,7 +36897,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34730,7 +36962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34791,7 +37027,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34852,7 +37092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34913,7 +37157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34974,7 +37222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35035,7 +37287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35096,7 +37352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35157,7 +37417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35218,7 +37482,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35279,7 +37547,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35340,7 +37612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35401,7 +37677,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35462,7 +37742,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35523,7 +37807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35584,7 +37872,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35645,7 +37937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35706,7 +38002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35767,7 +38067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35828,7 +38132,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35889,7 +38197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35950,7 +38262,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36011,7 +38327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36072,7 +38392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36133,7 +38457,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36194,7 +38522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36255,7 +38587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36316,7 +38652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36377,7 +38717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36438,7 +38782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36499,7 +38847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36560,7 +38912,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36621,7 +38977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36682,7 +39042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36743,7 +39107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36804,7 +39172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36865,7 +39237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36926,7 +39302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36987,7 +39367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37048,7 +39432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +39497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37170,7 +39562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37231,7 +39627,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37292,7 +39692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37353,7 +39757,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37414,7 +39822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37475,7 +39887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37536,7 +39952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37597,7 +40017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37658,7 +40082,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37719,7 +40147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37780,7 +40212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37841,7 +40277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37902,7 +40342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37963,7 +40407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38024,7 +40472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38085,7 +40537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38146,7 +40602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38207,7 +40667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38268,7 +40732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38329,7 +40797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38390,7 +40862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38451,7 +40927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38512,7 +40992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38573,7 +41057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38634,7 +41122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38695,7 +41187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38756,7 +41252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38817,7 +41317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38878,7 +41382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38939,7 +41447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39000,7 +41512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39061,7 +41577,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39122,7 +41642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39183,7 +41707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39244,7 +41772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39305,7 +41837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39366,7 +41902,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39427,7 +41967,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39488,7 +42032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39549,7 +42097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39610,7 +42162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39671,7 +42227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39732,7 +42292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39793,7 +42357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39854,7 +42422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39915,7 +42487,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39976,7 +42552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40037,7 +42617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40098,7 +42682,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40159,7 +42747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40220,7 +42812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40281,7 +42877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40342,7 +42942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40403,7 +43007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40464,7 +43072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40525,7 +43137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40586,7 +43202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40647,7 +43267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +43332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40769,7 +43397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40830,7 +43462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40891,7 +43527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +43592,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +43657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41074,7 +43722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41135,7 +43787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41196,7 +43852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41257,7 +43917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41318,7 +43982,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41379,7 +44047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41440,7 +44112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41501,7 +44177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41562,7 +44242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +44307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41684,7 +44372,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41745,7 +44437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41806,7 +44502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41867,7 +44567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41928,7 +44632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41989,7 +44697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42050,7 +44762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42111,7 +44827,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42172,7 +44892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42233,7 +44957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42294,7 +45022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42355,7 +45087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42416,7 +45152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42477,7 +45217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42538,7 +45282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42599,7 +45347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42660,7 +45412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42721,7 +45477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42782,7 +45542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42843,7 +45607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42904,7 +45672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42965,7 +45737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43026,7 +45802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43087,7 +45867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43148,7 +45932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43209,7 +45997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43270,7 +46062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43331,7 +46127,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43392,7 +46192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43453,7 +46257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43514,7 +46322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43575,7 +46387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43636,7 +46452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43697,7 +46517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43758,7 +46582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43819,7 +46647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43880,7 +46712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43941,7 +46777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44002,7 +46842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44063,7 +46907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44124,7 +46972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44185,7 +47037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44246,7 +47102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44307,7 +47167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +47232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44429,7 +47297,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44490,7 +47362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44551,7 +47427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44612,7 +47492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44673,7 +47557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44734,7 +47622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44795,7 +47687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44856,7 +47752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44917,7 +47817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44978,7 +47882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45039,7 +47947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45100,7 +48012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45161,7 +48077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +48142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45283,7 +48207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45344,7 +48272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45405,7 +48337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +48402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45527,7 +48467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45588,7 +48532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45649,7 +48597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45710,7 +48662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45771,7 +48727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45832,7 +48792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +48857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45954,7 +48922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46015,7 +48987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +49052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +49117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46198,7 +49182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46259,7 +49247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46320,7 +49312,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46381,7 +49377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46442,7 +49442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46503,7 +49507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46564,7 +49572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
